--- a/data/trans_orig/Q4504_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4504_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2007 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46803</t>
+          <t>47618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77885</t>
+          <t>77774</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38093</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>64547</t>
+          <t>65768</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92042</t>
+          <t>92448</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132215</t>
+          <t>132871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120708</t>
+          <t>120791</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>166223</t>
+          <t>163874</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>109732</t>
+          <t>111219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152645</t>
+          <t>153775</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>241831</t>
+          <t>242954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>301168</t>
+          <t>300325</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178200</t>
+          <t>175937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>223514</t>
+          <t>226244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>168287</t>
+          <t>167734</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214834</t>
+          <t>214742</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>356859</t>
+          <t>360501</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>424432</t>
+          <t>424732</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44882</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73832</t>
+          <t>72702</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66200</t>
+          <t>64059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98102</t>
+          <t>97486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116747</t>
+          <t>119164</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>160209</t>
+          <t>163921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>207540</t>
+          <t>209428</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257267</t>
+          <t>259095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210662</t>
+          <t>209738</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257856</t>
+          <t>257226</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>429749</t>
+          <t>436799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>498402</t>
+          <t>505501</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,62%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>151016</t>
+          <t>154262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202538</t>
+          <t>205613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140804</t>
+          <t>137411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>187210</t>
+          <t>189304</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306572</t>
+          <t>306986</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>377667</t>
+          <t>375411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>135179</t>
+          <t>133679</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181755</t>
+          <t>181271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115564</t>
+          <t>117702</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160405</t>
+          <t>162647</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265639</t>
+          <t>263955</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>329176</t>
+          <t>328107</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264622</t>
+          <t>264870</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324240</t>
+          <t>324101</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252190</t>
+          <t>252855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>309228</t>
+          <t>307066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>535026</t>
+          <t>530338</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>617114</t>
+          <t>616999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63668</t>
+          <t>64261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98413</t>
+          <t>98246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64300</t>
+          <t>65448</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98677</t>
+          <t>99196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137331</t>
+          <t>137544</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>185508</t>
+          <t>186587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>227507</t>
+          <t>226023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>283346</t>
+          <t>281079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>277239</t>
+          <t>273849</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>336276</t>
+          <t>333825</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521678</t>
+          <t>515167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>600264</t>
+          <t>601253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,2%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93820</t>
+          <t>92025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132696</t>
+          <t>132804</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>124011</t>
+          <t>121731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166635</t>
+          <t>165566</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>225168</t>
+          <t>226503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>282600</t>
+          <t>283944</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142324</t>
+          <t>142784</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188014</t>
+          <t>188622</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118856</t>
+          <t>120399</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>162097</t>
+          <t>160576</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>274095</t>
+          <t>269672</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335412</t>
+          <t>331969</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>162813</t>
+          <t>164535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>211732</t>
+          <t>212538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>127199</t>
+          <t>125184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>168765</t>
+          <t>167475</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>298187</t>
+          <t>300578</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>363184</t>
+          <t>366040</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40830</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>70210</t>
+          <t>69442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>33131</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59071</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80759</t>
+          <t>79354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121346</t>
+          <t>119212</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>139137</t>
+          <t>140935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>185067</t>
+          <t>186101</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>189055</t>
+          <t>187239</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235854</t>
+          <t>236361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341300</t>
+          <t>341179</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>405905</t>
+          <t>407360</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>166003</t>
+          <t>167134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215701</t>
+          <t>215413</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217106</t>
+          <t>217314</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272660</t>
+          <t>272377</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>395249</t>
+          <t>395559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>471304</t>
+          <t>470222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,75%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>212379</t>
+          <t>213330</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>263764</t>
+          <t>262798</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195186</t>
+          <t>195897</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>249965</t>
+          <t>251833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>421858</t>
+          <t>421686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>496450</t>
+          <t>497832</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>234782</t>
+          <t>236208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>286658</t>
+          <t>287748</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>220535</t>
+          <t>217931</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>276454</t>
+          <t>276598</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>475089</t>
+          <t>473717</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>550796</t>
+          <t>549481</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54599</t>
+          <t>54182</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85769</t>
+          <t>84593</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57750</t>
+          <t>54793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89904</t>
+          <t>89194</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>116353</t>
+          <t>119859</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161795</t>
+          <t>162867</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>165208</t>
+          <t>163004</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209646</t>
+          <t>209832</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>223213</t>
+          <t>226125</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>280579</t>
+          <t>281856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>398020</t>
+          <t>404919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>476954</t>
+          <t>476183</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>497255</t>
+          <t>500729</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>584212</t>
+          <t>582085</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>554898</t>
+          <t>555915</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>648036</t>
+          <t>643931</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1076116</t>
+          <t>1071540</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1203578</t>
+          <t>1198878</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>651973</t>
+          <t>647740</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>746797</t>
+          <t>744516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>585760</t>
+          <t>582263</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>672713</t>
+          <t>673790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1263679</t>
+          <t>1262716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1405563</t>
+          <t>1389345</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>894400</t>
+          <t>893390</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1000849</t>
+          <t>995254</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>820209</t>
+          <t>814692</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>916763</t>
+          <t>914552</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1741004</t>
+          <t>1733784</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1878366</t>
+          <t>1887929</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>231456</t>
+          <t>231226</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>295824</t>
+          <t>292313</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>247858</t>
+          <t>250591</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>309786</t>
+          <t>311091</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>494825</t>
+          <t>492873</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>583761</t>
+          <t>586664</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>787668</t>
+          <t>783087</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>887930</t>
+          <t>886949</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>951819</t>
+          <t>948067</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1058618</t>
+          <t>1055643</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1766225</t>
+          <t>1763865</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1915202</t>
+          <t>1914416</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2012 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132282</t>
+          <t>130709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175103</t>
+          <t>175639</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108367</t>
+          <t>108938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>152669</t>
+          <t>150121</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>252632</t>
+          <t>251554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>310631</t>
+          <t>312540</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>124761</t>
+          <t>126596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168897</t>
+          <t>169682</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127785</t>
+          <t>130339</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>174118</t>
+          <t>171860</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265703</t>
+          <t>267691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329784</t>
+          <t>326920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>109774</t>
+          <t>108373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149553</t>
+          <t>149765</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>108271</t>
+          <t>110382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151552</t>
+          <t>153014</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230299</t>
+          <t>232283</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>289006</t>
+          <t>290893</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>22735</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47149</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26450</t>
+          <t>26978</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>54321</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>91487</t>
+          <t>87399</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>214727</t>
+          <t>212562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265386</t>
+          <t>265401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222361</t>
+          <t>225850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278837</t>
+          <t>277566</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>453641</t>
+          <t>454048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>525582</t>
+          <t>528962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>224583</t>
+          <t>226262</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>282642</t>
+          <t>283802</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210440</t>
+          <t>211624</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268525</t>
+          <t>267261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>450051</t>
+          <t>451452</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>531607</t>
+          <t>532012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,06%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168075</t>
+          <t>164250</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218316</t>
+          <t>218073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>184435</t>
+          <t>185103</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>238545</t>
+          <t>239423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364975</t>
+          <t>364943</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>441040</t>
+          <t>440459</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169341</t>
+          <t>169509</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>218164</t>
+          <t>221497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169553</t>
+          <t>169225</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>220397</t>
+          <t>222545</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>351918</t>
+          <t>350482</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>422277</t>
+          <t>421906</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>34820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63595</t>
+          <t>63295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33393</t>
+          <t>33819</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>60710</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75649</t>
+          <t>77178</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115500</t>
+          <t>118964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>300821</t>
+          <t>299585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>364115</t>
+          <t>361158</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305145</t>
+          <t>303141</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370395</t>
+          <t>367119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>623292</t>
+          <t>622819</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>709483</t>
+          <t>710298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144648</t>
+          <t>146377</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194488</t>
+          <t>195217</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>141560</t>
+          <t>139336</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>188982</t>
+          <t>189561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>300772</t>
+          <t>300132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>371972</t>
+          <t>367359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,04%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>133624</t>
+          <t>132249</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178474</t>
+          <t>178550</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>152242</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200107</t>
+          <t>200062</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>292125</t>
+          <t>295490</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361859</t>
+          <t>362438</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>138145</t>
+          <t>137327</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>186496</t>
+          <t>185667</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123490</t>
+          <t>123187</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166194</t>
+          <t>169142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>269467</t>
+          <t>273430</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>338347</t>
+          <t>336353</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33012</t>
+          <t>34392</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15337</t>
+          <t>15068</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33832</t>
+          <t>34008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62679</t>
+          <t>62789</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>219688</t>
+          <t>221295</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273767</t>
+          <t>273596</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240494</t>
+          <t>240841</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295685</t>
+          <t>295887</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474174</t>
+          <t>477383</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>551817</t>
+          <t>552020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>274634</t>
+          <t>273448</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>329192</t>
+          <t>332530</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>311222</t>
+          <t>313535</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>376392</t>
+          <t>375223</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>607950</t>
+          <t>604385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>692389</t>
+          <t>686875</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,42%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>231052</t>
+          <t>227065</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>284423</t>
+          <t>283551</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>236623</t>
+          <t>239423</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>296727</t>
+          <t>297854</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480001</t>
+          <t>480388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>560151</t>
+          <t>562392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>147046</t>
+          <t>146268</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>194187</t>
+          <t>195786</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>144951</t>
+          <t>144354</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>195161</t>
+          <t>194302</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>301918</t>
+          <t>302545</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>372258</t>
+          <t>371372</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28071</t>
+          <t>26698</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53978</t>
+          <t>51049</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30920</t>
+          <t>31171</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>55997</t>
+          <t>56703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>64792</t>
+          <t>65408</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>100542</t>
+          <t>99477</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>159523</t>
+          <t>158702</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>207987</t>
+          <t>206923</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>199187</t>
+          <t>196857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>252943</t>
+          <t>254161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>370904</t>
+          <t>373198</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>444258</t>
+          <t>448932</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>825727</t>
+          <t>826324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>929774</t>
+          <t>935930</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>823309</t>
+          <t>822238</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>927464</t>
+          <t>923667</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1685302</t>
+          <t>1677086</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1840555</t>
+          <t>1826252</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>694861</t>
+          <t>696729</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>801713</t>
+          <t>795890</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>753309</t>
+          <t>752303</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>852247</t>
+          <t>853561</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1483878</t>
+          <t>1482770</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1619179</t>
+          <t>1620628</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>605142</t>
+          <t>604269</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>697173</t>
+          <t>699420</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>591560</t>
+          <t>589421</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>688709</t>
+          <t>684768</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1223009</t>
+          <t>1219204</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1360398</t>
+          <t>1355696</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>120123</t>
+          <t>120816</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>168860</t>
+          <t>168025</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>127856</t>
+          <t>125723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>175505</t>
+          <t>176014</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>263728</t>
+          <t>258747</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>332670</t>
+          <t>324496</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>944354</t>
+          <t>948827</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1050247</t>
+          <t>1052924</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1030364</t>
+          <t>1025483</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1145742</t>
+          <t>1141226</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2000723</t>
+          <t>2002942</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2153900</t>
+          <t>2160258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,02%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron la sombra para evitar el sol el pasado verano al aire libre en 2016 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109104</t>
+          <t>109784</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149368</t>
+          <t>149380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,7 +8031,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>103786</t>
+          <t>105649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>145456</t>
+          <t>146581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>227272</t>
+          <t>226654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>283241</t>
+          <t>282659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,01%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130771</t>
+          <t>131417</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>173385</t>
+          <t>175828</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147658</t>
+          <t>151285</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194507</t>
+          <t>194328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>291117</t>
+          <t>295108</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>357921</t>
+          <t>356896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,53%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108999</t>
+          <t>105753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152482</t>
+          <t>147907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>109165</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>150501</t>
+          <t>150824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230355</t>
+          <t>230457</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>286157</t>
+          <t>290265</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,57%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>32856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58797</t>
+          <t>59257</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57267</t>
+          <t>56580</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71168</t>
+          <t>72617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108070</t>
+          <t>109210</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>195412</t>
+          <t>197878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>243708</t>
+          <t>245971</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177812</t>
+          <t>180008</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>226191</t>
+          <t>226195</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>390550</t>
+          <t>391083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>461229</t>
+          <t>457217</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>163769</t>
+          <t>162314</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>213909</t>
+          <t>214549</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>200660</t>
+          <t>201597</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>255781</t>
+          <t>256079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>375811</t>
+          <t>374367</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>454651</t>
+          <t>452263</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>321875</t>
+          <t>325753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>383368</t>
+          <t>386801</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>333037</t>
+          <t>332321</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>395295</t>
+          <t>393446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669258</t>
+          <t>671777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>755742</t>
+          <t>759702</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,72%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>116106</t>
+          <t>115798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>161110</t>
+          <t>160322</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113813</t>
+          <t>115485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155890</t>
+          <t>157186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>244803</t>
+          <t>242663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>307401</t>
+          <t>303283</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,74%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38864</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68039</t>
+          <t>67050</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40044</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>68510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84675</t>
+          <t>85969</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125758</t>
+          <t>127209</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260997</t>
+          <t>259741</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>318284</t>
+          <t>320310</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>235332</t>
+          <t>234881</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294267</t>
+          <t>292079</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>513972</t>
+          <t>508896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>593729</t>
+          <t>589122</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106963</t>
+          <t>106168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145595</t>
+          <t>146852</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>148168</t>
+          <t>151383</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197910</t>
+          <t>197635</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>266827</t>
+          <t>268981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>330719</t>
+          <t>335391</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267632</t>
+          <t>270931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>324001</t>
+          <t>324108</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>287658</t>
+          <t>287710</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>344345</t>
+          <t>341754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>567209</t>
+          <t>571933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>647207</t>
+          <t>651932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,48%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>127843</t>
+          <t>125282</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>173346</t>
+          <t>170321</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>108256</t>
+          <t>105661</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>148559</t>
+          <t>147166</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>243680</t>
+          <t>245098</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>306954</t>
+          <t>306125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21696</t>
+          <t>21120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43664</t>
+          <t>43148</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14728</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35625</t>
+          <t>34587</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>40588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71364</t>
+          <t>72606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>136011</t>
+          <t>132251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181239</t>
+          <t>180372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120744</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>167405</t>
+          <t>163618</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265118</t>
+          <t>265101</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>327601</t>
+          <t>332834</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>254430</t>
+          <t>255210</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>310481</t>
+          <t>309193</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>319352</t>
+          <t>319896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>380494</t>
+          <t>380380</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586832</t>
+          <t>588954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>674700</t>
+          <t>672053</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236575</t>
+          <t>236969</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289936</t>
+          <t>289330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>242865</t>
+          <t>238809</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>298828</t>
+          <t>298087</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>494798</t>
+          <t>498475</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>573342</t>
+          <t>572138</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>125435</t>
+          <t>126785</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>170760</t>
+          <t>170625</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>116208</t>
+          <t>117159</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>161617</t>
+          <t>163871</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>257165</t>
+          <t>256332</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>318519</t>
+          <t>317210</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29993</t>
+          <t>29782</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55961</t>
+          <t>55380</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40246</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69840</t>
+          <t>69334</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78824</t>
+          <t>77918</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>117968</t>
+          <t>114593</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>179140</t>
+          <t>176816</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>229605</t>
+          <t>226613</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>202699</t>
+          <t>202721</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>257386</t>
+          <t>257013</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>394911</t>
+          <t>393434</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>469510</t>
+          <t>475609</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>672025</t>
+          <t>678695</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>772747</t>
+          <t>776913</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>825720</t>
+          <t>824071</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>927544</t>
+          <t>931153</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1530641</t>
+          <t>1522238</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1677137</t>
+          <t>1668849</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1005673</t>
+          <t>1011718</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1119327</t>
+          <t>1117573</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1062537</t>
+          <t>1065966</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1174781</t>
+          <t>1175792</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2105574</t>
+          <t>2093434</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2265086</t>
+          <t>2255876</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>515880</t>
+          <t>518272</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>605742</t>
+          <t>607819</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>488494</t>
+          <t>489714</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>574550</t>
+          <t>575239</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1028635</t>
+          <t>1032119</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1152150</t>
+          <t>1156866</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,73%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>145496</t>
+          <t>144345</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>198841</t>
+          <t>199207</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>148390</t>
+          <t>149304</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>198214</t>
+          <t>200963</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306769</t>
+          <t>306848</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>383352</t>
+          <t>380966</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>816058</t>
+          <t>812053</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>925927</t>
+          <t>912893</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>786287</t>
+          <t>781549</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>890568</t>
+          <t>890748</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1625493</t>
+          <t>1618545</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1780753</t>
+          <t>1782407</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4504_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q4504_R-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47618</t>
+          <t>47069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77774</t>
+          <t>76665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>38686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>65768</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>92448</t>
+          <t>91193</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>132871</t>
+          <t>131265</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120791</t>
+          <t>121485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>163874</t>
+          <t>163445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>111219</t>
+          <t>108010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>153775</t>
+          <t>151378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242954</t>
+          <t>241194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300325</t>
+          <t>300873</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175937</t>
+          <t>177509</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226244</t>
+          <t>223130</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167734</t>
+          <t>169723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>214742</t>
+          <t>212023</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>360501</t>
+          <t>362476</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>424732</t>
+          <t>426904</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>44082</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72702</t>
+          <t>72561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64059</t>
+          <t>65541</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97486</t>
+          <t>98378</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119164</t>
+          <t>119413</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163921</t>
+          <t>163117</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209428</t>
+          <t>207537</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>259095</t>
+          <t>257887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>209738</t>
+          <t>207164</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257226</t>
+          <t>257118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>436799</t>
+          <t>432802</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505501</t>
+          <t>502438</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,4%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>154262</t>
+          <t>151747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>205613</t>
+          <t>206454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137411</t>
+          <t>140582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>189304</t>
+          <t>187813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>306986</t>
+          <t>306346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>375411</t>
+          <t>377410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133679</t>
+          <t>134529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>181271</t>
+          <t>179952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117702</t>
+          <t>119109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>162647</t>
+          <t>162155</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263955</t>
+          <t>265326</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>328107</t>
+          <t>333825</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>264870</t>
+          <t>266330</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>324101</t>
+          <t>322062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>252855</t>
+          <t>252690</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>307066</t>
+          <t>309832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>530338</t>
+          <t>537634</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>616999</t>
+          <t>621708</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64261</t>
+          <t>64013</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98246</t>
+          <t>97701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65448</t>
+          <t>64117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99196</t>
+          <t>101804</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137544</t>
+          <t>138357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186587</t>
+          <t>185803</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226023</t>
+          <t>226635</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>281079</t>
+          <t>283819</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>273849</t>
+          <t>277157</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333825</t>
+          <t>332283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>515167</t>
+          <t>520142</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>601253</t>
+          <t>600674</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,17%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>92025</t>
+          <t>92159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132804</t>
+          <t>134490</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121731</t>
+          <t>122761</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>165566</t>
+          <t>162514</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>226503</t>
+          <t>225785</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>283944</t>
+          <t>283937</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>142784</t>
+          <t>140353</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188622</t>
+          <t>188689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120399</t>
+          <t>119497</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>160576</t>
+          <t>158964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269672</t>
+          <t>273082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>331969</t>
+          <t>335753</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,66%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>164535</t>
+          <t>163664</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>212538</t>
+          <t>213323</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>125184</t>
+          <t>125315</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>167475</t>
+          <t>166686</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>300578</t>
+          <t>298203</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>366040</t>
+          <t>364002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69442</t>
+          <t>69475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33131</t>
+          <t>33664</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58642</t>
+          <t>60087</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79354</t>
+          <t>80660</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119212</t>
+          <t>118611</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>140935</t>
+          <t>139278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>186101</t>
+          <t>184916</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>187239</t>
+          <t>187496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>236361</t>
+          <t>235658</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>341179</t>
+          <t>345219</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>407360</t>
+          <t>408552</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167134</t>
+          <t>166707</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>215413</t>
+          <t>215466</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>217314</t>
+          <t>216649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>272377</t>
+          <t>272815</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>395559</t>
+          <t>398504</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>470222</t>
+          <t>474078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>213330</t>
+          <t>210590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>262798</t>
+          <t>263978</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>195897</t>
+          <t>196736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>251833</t>
+          <t>248317</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>421686</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>497832</t>
+          <t>496742</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>236208</t>
+          <t>235509</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>287748</t>
+          <t>288713</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>217931</t>
+          <t>219218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>276598</t>
+          <t>275615</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>473717</t>
+          <t>472406</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>549481</t>
+          <t>550468</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54182</t>
+          <t>53906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84593</t>
+          <t>85383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54793</t>
+          <t>57287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89194</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119859</t>
+          <t>118759</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>162867</t>
+          <t>164488</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>163004</t>
+          <t>162451</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>209832</t>
+          <t>209843</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>226125</t>
+          <t>224780</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>281856</t>
+          <t>278937</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>404919</t>
+          <t>402758</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>476183</t>
+          <t>481398</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>500729</t>
+          <t>496619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>582085</t>
+          <t>586396</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>555915</t>
+          <t>552905</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>643931</t>
+          <t>637208</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1071540</t>
+          <t>1075930</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1198878</t>
+          <t>1199010</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>647740</t>
+          <t>655151</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>744516</t>
+          <t>747585</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>582263</t>
+          <t>583982</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>673790</t>
+          <t>674178</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1262716</t>
+          <t>1263783</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1389345</t>
+          <t>1392310</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,94%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>893390</t>
+          <t>892981</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>995254</t>
+          <t>997209</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>814692</t>
+          <t>814872</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>914552</t>
+          <t>916760</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1733784</t>
+          <t>1731364</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1887929</t>
+          <t>1875539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>231226</t>
+          <t>230847</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>292313</t>
+          <t>293617</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>250591</t>
+          <t>246548</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>311091</t>
+          <t>311632</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>492873</t>
+          <t>493449</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>586664</t>
+          <t>580972</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>783087</t>
+          <t>783577</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>886949</t>
+          <t>882824</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>948067</t>
+          <t>951724</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1055643</t>
+          <t>1056831</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1763865</t>
+          <t>1772306</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1914416</t>
+          <t>1918951</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130709</t>
+          <t>130800</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175639</t>
+          <t>176512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108938</t>
+          <t>109095</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>150121</t>
+          <t>149412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251554</t>
+          <t>248638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>312540</t>
+          <t>310891</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126596</t>
+          <t>125224</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169682</t>
+          <t>172719</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>130339</t>
+          <t>127848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171860</t>
+          <t>173317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>267691</t>
+          <t>266305</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>326920</t>
+          <t>330841</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>108373</t>
+          <t>108232</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>149765</t>
+          <t>149480</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>110382</t>
+          <t>108678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>153014</t>
+          <t>149482</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232283</t>
+          <t>228258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290893</t>
+          <t>287641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22735</t>
+          <t>23558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>47145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>26740</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50406</t>
+          <t>52347</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54321</t>
+          <t>54974</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>87399</t>
+          <t>88034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212562</t>
+          <t>217525</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>265401</t>
+          <t>267994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>225850</t>
+          <t>223962</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277566</t>
+          <t>278425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>454048</t>
+          <t>453971</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>528962</t>
+          <t>529437</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>226262</t>
+          <t>225850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>283802</t>
+          <t>281824</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211624</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>267261</t>
+          <t>269068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>451452</t>
+          <t>452336</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>532012</t>
+          <t>531255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,02%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>164250</t>
+          <t>166277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218073</t>
+          <t>218642</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>185103</t>
+          <t>182179</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239423</t>
+          <t>238300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364943</t>
+          <t>364843</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>440459</t>
+          <t>440293</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,56%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>169509</t>
+          <t>167531</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>221497</t>
+          <t>217940</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>169225</t>
+          <t>168078</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>222545</t>
+          <t>220294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>350482</t>
+          <t>352974</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>421906</t>
+          <t>422584</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34820</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63295</t>
+          <t>64684</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33819</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60710</t>
+          <t>61663</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>77178</t>
+          <t>76832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118964</t>
+          <t>114552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>299585</t>
+          <t>298236</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>361158</t>
+          <t>360384</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>303141</t>
+          <t>309823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>367119</t>
+          <t>368185</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>622819</t>
+          <t>624940</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>710298</t>
+          <t>710787</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>146377</t>
+          <t>146245</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>195217</t>
+          <t>194313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>139336</t>
+          <t>139918</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>189561</t>
+          <t>191217</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>300132</t>
+          <t>301001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367359</t>
+          <t>367680</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>131594</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178550</t>
+          <t>178619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>152242</t>
+          <t>150067</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200062</t>
+          <t>197457</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>295490</t>
+          <t>296171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>362438</t>
+          <t>361501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137327</t>
+          <t>138497</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>185667</t>
+          <t>186800</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>123187</t>
+          <t>120578</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>169142</t>
+          <t>166494</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>273430</t>
+          <t>274363</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>336353</t>
+          <t>338893</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,18%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14742</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34392</t>
+          <t>34506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,47 +6092,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>23431</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>14612</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>34127</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>1,89%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>23431</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>15068</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>35692</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,03%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>33182</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62789</t>
+          <t>60838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221295</t>
+          <t>217215</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>273596</t>
+          <t>272372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>240841</t>
+          <t>240594</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>295887</t>
+          <t>297615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>477383</t>
+          <t>472586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>552020</t>
+          <t>553053</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>273448</t>
+          <t>273620</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>332530</t>
+          <t>330225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>313535</t>
+          <t>314430</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>375223</t>
+          <t>376443</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>604385</t>
+          <t>601490</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>686875</t>
+          <t>687591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>227065</t>
+          <t>226720</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>283551</t>
+          <t>283929</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>239423</t>
+          <t>238889</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>297854</t>
+          <t>296300</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480388</t>
+          <t>485339</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>562392</t>
+          <t>566200</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>146268</t>
+          <t>146499</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>195786</t>
+          <t>196575</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>144354</t>
+          <t>144287</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>194302</t>
+          <t>189804</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>302545</t>
+          <t>303726</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>371372</t>
+          <t>371737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,63%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26698</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51049</t>
+          <t>52987</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31171</t>
+          <t>31740</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56703</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>65408</t>
+          <t>66343</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99477</t>
+          <t>100049</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>158702</t>
+          <t>157887</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>206923</t>
+          <t>209919</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>196857</t>
+          <t>199368</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>254161</t>
+          <t>251843</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>373198</t>
+          <t>375523</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>448932</t>
+          <t>448362</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,47%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>826324</t>
+          <t>821868</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>935930</t>
+          <t>935338</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>822238</t>
+          <t>821589</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>923667</t>
+          <t>932685</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1677086</t>
+          <t>1682088</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1826252</t>
+          <t>1834693</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,35%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>696729</t>
+          <t>698304</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>795890</t>
+          <t>800065</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>752303</t>
+          <t>751978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>853561</t>
+          <t>852945</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1482770</t>
+          <t>1480349</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1620628</t>
+          <t>1623846</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>604269</t>
+          <t>602725</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>699420</t>
+          <t>704625</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>589421</t>
+          <t>592424</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>684768</t>
+          <t>685923</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1219204</t>
+          <t>1228997</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1355696</t>
+          <t>1355456</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,7 +7413,7 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>120816</t>
+          <t>118989</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>168025</t>
+          <t>168049</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>125723</t>
+          <t>126812</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>176014</t>
+          <t>174677</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>258747</t>
+          <t>259409</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>324496</t>
+          <t>325784</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>948827</t>
+          <t>938448</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1052924</t>
+          <t>1054249</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1025483</t>
+          <t>1017495</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>1141226</t>
+          <t>1133764</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2002942</t>
+          <t>1997143</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2160258</t>
+          <t>2154229</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109784</t>
+          <t>106808</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>149380</t>
+          <t>150779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105649</t>
+          <t>105534</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146581</t>
+          <t>145625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>226654</t>
+          <t>225261</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>282659</t>
+          <t>283644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,08%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131417</t>
+          <t>132821</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175828</t>
+          <t>176578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>151285</t>
+          <t>148986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194328</t>
+          <t>193613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>295108</t>
+          <t>292999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356896</t>
+          <t>356927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,7 +8214,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>105753</t>
+          <t>109526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>147907</t>
+          <t>150630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109165</t>
+          <t>109251</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>149542</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>230457</t>
+          <t>230066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>290265</t>
+          <t>285114</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32856</t>
+          <t>32998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59257</t>
+          <t>59397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>31277</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56580</t>
+          <t>58413</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>71571</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109210</t>
+          <t>108523</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>197878</t>
+          <t>196845</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245971</t>
+          <t>246180</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180008</t>
+          <t>179848</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>226195</t>
+          <t>228026</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>391083</t>
+          <t>387501</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>457217</t>
+          <t>459017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>162314</t>
+          <t>162059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>214549</t>
+          <t>211621</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>201597</t>
+          <t>202786</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>256079</t>
+          <t>256634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>374367</t>
+          <t>378869</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>452263</t>
+          <t>452826</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>325753</t>
+          <t>320459</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>386801</t>
+          <t>384805</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>332321</t>
+          <t>328607</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>393446</t>
+          <t>393951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671777</t>
+          <t>671844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>759702</t>
+          <t>760616</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,96%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115798</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>160322</t>
+          <t>161998</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115485</t>
+          <t>114794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157186</t>
+          <t>160899</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>242663</t>
+          <t>244062</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303283</t>
+          <t>307818</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36881</t>
+          <t>39205</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67050</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>39700</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68510</t>
+          <t>69641</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85969</t>
+          <t>86755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127209</t>
+          <t>126407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>259741</t>
+          <t>259088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>320310</t>
+          <t>316551</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234881</t>
+          <t>234646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>292079</t>
+          <t>293080</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>508896</t>
+          <t>512209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>589122</t>
+          <t>591049</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106168</t>
+          <t>103914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>146852</t>
+          <t>148655</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151383</t>
+          <t>150778</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>197635</t>
+          <t>198690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268981</t>
+          <t>268810</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>335391</t>
+          <t>333946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>270931</t>
+          <t>269574</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>324108</t>
+          <t>324143</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>287710</t>
+          <t>285085</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>341754</t>
+          <t>343638</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>571933</t>
+          <t>566820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>651932</t>
+          <t>649683</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125282</t>
+          <t>124933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>170321</t>
+          <t>170496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>105661</t>
+          <t>108184</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>147166</t>
+          <t>151779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>245098</t>
+          <t>242616</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>306125</t>
+          <t>305710</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,92%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21120</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43148</t>
+          <t>44466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34587</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40588</t>
+          <t>41053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72606</t>
+          <t>70412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>132251</t>
+          <t>133570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>180372</t>
+          <t>180078</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>118681</t>
+          <t>120840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>163618</t>
+          <t>166231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>265101</t>
+          <t>267462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>332834</t>
+          <t>330772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>255210</t>
+          <t>253727</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>309193</t>
+          <t>312403</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>319896</t>
+          <t>318392</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>380380</t>
+          <t>381813</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>588954</t>
+          <t>591583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>672053</t>
+          <t>675717</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236969</t>
+          <t>239445</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>289330</t>
+          <t>296314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>238809</t>
+          <t>244212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>298087</t>
+          <t>299039</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>498475</t>
+          <t>493704</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>572138</t>
+          <t>575549</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,1%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>126785</t>
+          <t>128713</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>170625</t>
+          <t>171603</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>117236</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163871</t>
+          <t>159929</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>256332</t>
+          <t>257031</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>317210</t>
+          <t>320044</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,18%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29782</t>
+          <t>30735</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55380</t>
+          <t>56679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>69334</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,47 +10451,47 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>6,82%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>95157</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>76622</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>115186</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>3,87%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>95157</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>77918</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>114593</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>3,94%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>176816</t>
+          <t>176564</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>226613</t>
+          <t>226412</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>202721</t>
+          <t>203204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>257013</t>
+          <t>261131</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>393434</t>
+          <t>392928</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>475609</t>
+          <t>470419</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>678695</t>
+          <t>676370</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>776913</t>
+          <t>772237</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>824071</t>
+          <t>827046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>931153</t>
+          <t>932625</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1522238</t>
+          <t>1527845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1668849</t>
+          <t>1679601</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1011718</t>
+          <t>1004999</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1117573</t>
+          <t>1117810</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1065966</t>
+          <t>1062577</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1175792</t>
+          <t>1179753</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2093434</t>
+          <t>2108055</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2255876</t>
+          <t>2264799</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,75%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>518272</t>
+          <t>519190</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>607819</t>
+          <t>608256</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>489714</t>
+          <t>486515</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>575239</t>
+          <t>573036</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1032119</t>
+          <t>1024935</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1156866</t>
+          <t>1150161</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,63%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>144345</t>
+          <t>145158</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>199207</t>
+          <t>194610</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>149304</t>
+          <t>148996</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>200963</t>
+          <t>199291</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11138,7 +11138,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306848</t>
+          <t>310456</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>380966</t>
+          <t>383869</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>812053</t>
+          <t>815131</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>912893</t>
+          <t>911605</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>781549</t>
+          <t>785176</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>890748</t>
+          <t>892496</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1618545</t>
+          <t>1629691</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1782407</t>
+          <t>1787873</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
